--- a/new-app/sample-data/401k/pass/expected-output/ValAssemblyLog.xlsx
+++ b/new-app/sample-data/401k/pass/expected-output/ValAssemblyLog.xlsx
@@ -880,12 +880,12 @@
       <c r="U3" s="5" t="n"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>10/21/2026 5:56 PM</t>
+          <t>10/21/2026 6:27 PM</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>6 sec</t>
+          <t>5 sec</t>
         </is>
       </c>
     </row>

--- a/new-app/sample-data/401k/pass/expected-output/ValAssemblyLog.xlsx
+++ b/new-app/sample-data/401k/pass/expected-output/ValAssemblyLog.xlsx
@@ -880,12 +880,12 @@
       <c r="U3" s="5" t="n"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>10/21/2026 6:27 PM</t>
+          <t>10/22/2026 8:12 PM</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>5 sec</t>
+          <t>7 sec</t>
         </is>
       </c>
     </row>
